--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/112.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/112.xlsx
@@ -426,13 +426,13 @@
         <v>-16.8036317449496</v>
       </c>
       <c r="E2">
-        <v>-17.40314958341116</v>
+        <v>-18.49304006520723</v>
       </c>
       <c r="F2">
-        <v>-4.002052647124827</v>
+        <v>-4.50307907356447</v>
       </c>
       <c r="G2">
-        <v>-11.06262275160865</v>
+        <v>-10.80823712182551</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.09364986024373</v>
       </c>
       <c r="E3">
-        <v>-18.28876513119522</v>
+        <v>-19.9036959463886</v>
       </c>
       <c r="F3">
-        <v>-4.187321986965354</v>
+        <v>-4.857578903592517</v>
       </c>
       <c r="G3">
-        <v>-11.37380410066352</v>
+        <v>-11.31734605703679</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.44154742986373</v>
       </c>
       <c r="E4">
-        <v>-17.30489075439273</v>
+        <v>-18.55902445997299</v>
       </c>
       <c r="F4">
-        <v>-4.048552222913576</v>
+        <v>-4.550706885755829</v>
       </c>
       <c r="G4">
-        <v>-10.74559497913142</v>
+        <v>-11.29819124054657</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.78348210193197</v>
       </c>
       <c r="E5">
-        <v>-18.75200537980986</v>
+        <v>-19.1474679579517</v>
       </c>
       <c r="F5">
-        <v>-3.97391631992134</v>
+        <v>-4.34378567874093</v>
       </c>
       <c r="G5">
-        <v>-10.14374773172854</v>
+        <v>-10.83842267605259</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.07782824751837</v>
       </c>
       <c r="E6">
-        <v>-19.23161153348822</v>
+        <v>-20.24178275885325</v>
       </c>
       <c r="F6">
-        <v>-4.246952842823279</v>
+        <v>-4.529905751904131</v>
       </c>
       <c r="G6">
-        <v>-9.770609522906206</v>
+        <v>-10.45192972652483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.28988443289133</v>
       </c>
       <c r="E7">
-        <v>-19.286387955085</v>
+        <v>-20.32802301785533</v>
       </c>
       <c r="F7">
-        <v>-3.779816583566971</v>
+        <v>-4.57557116171826</v>
       </c>
       <c r="G7">
-        <v>-9.985354680402109</v>
+        <v>-11.13849714482321</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.39807697033682</v>
       </c>
       <c r="E8">
-        <v>-19.02054388846472</v>
+        <v>-20.1747975713318</v>
       </c>
       <c r="F8">
-        <v>-4.52333928350214</v>
+        <v>-4.492950625330439</v>
       </c>
       <c r="G8">
-        <v>-11.51747846652235</v>
+        <v>-10.39225052208839</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.36785606125277</v>
       </c>
       <c r="E9">
-        <v>-20.73322634358767</v>
+        <v>-20.94588801146188</v>
       </c>
       <c r="F9">
-        <v>-3.680368591758682</v>
+        <v>-3.856610383643499</v>
       </c>
       <c r="G9">
-        <v>-9.213252697005586</v>
+        <v>-10.07240547535724</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.1767045100382</v>
       </c>
       <c r="E10">
-        <v>-22.72080981334625</v>
+        <v>-20.8411715785085</v>
       </c>
       <c r="F10">
-        <v>-3.915749189264161</v>
+        <v>-4.08812416211271</v>
       </c>
       <c r="G10">
-        <v>-9.155887563901096</v>
+        <v>-10.58447734882617</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.83108121916535</v>
       </c>
       <c r="E11">
-        <v>-20.64209986113132</v>
+        <v>-21.83970009719982</v>
       </c>
       <c r="F11">
-        <v>-3.687067598945121</v>
+        <v>-3.996551459202836</v>
       </c>
       <c r="G11">
-        <v>-9.951593736992622</v>
+        <v>-11.18982715340961</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.33572969994422</v>
       </c>
       <c r="E12">
-        <v>-20.18106497935841</v>
+        <v>-21.91565166325647</v>
       </c>
       <c r="F12">
-        <v>-3.951225680023855</v>
+        <v>-4.146981322816421</v>
       </c>
       <c r="G12">
-        <v>-9.355745198106897</v>
+        <v>-10.39752753167799</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.69159668328747</v>
       </c>
       <c r="E13">
-        <v>-22.09529622714075</v>
+        <v>-22.21400111630381</v>
       </c>
       <c r="F13">
-        <v>-3.963388598599161</v>
+        <v>-3.549812918873063</v>
       </c>
       <c r="G13">
-        <v>-9.416165964744136</v>
+        <v>-10.50879165670736</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.94353531034915</v>
       </c>
       <c r="E14">
-        <v>-22.39975006315044</v>
+        <v>-22.55108260753876</v>
       </c>
       <c r="F14">
-        <v>-3.187987007534656</v>
+        <v>-3.708952237359681</v>
       </c>
       <c r="G14">
-        <v>-8.981001374698016</v>
+        <v>-9.153619840206694</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.13051058582124</v>
       </c>
       <c r="E15">
-        <v>-21.5567746266226</v>
+        <v>-22.89690405360852</v>
       </c>
       <c r="F15">
-        <v>-3.277329745396194</v>
+        <v>-3.455972974381726</v>
       </c>
       <c r="G15">
-        <v>-8.422734148774099</v>
+        <v>-9.346763688058854</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.28556260417995</v>
       </c>
       <c r="E16">
-        <v>-22.7028317715358</v>
+        <v>-23.03281714400073</v>
       </c>
       <c r="F16">
-        <v>-2.925802097609389</v>
+        <v>-3.337895828051879</v>
       </c>
       <c r="G16">
-        <v>-8.046705833695981</v>
+        <v>-8.541741639819818</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.45918289724925</v>
       </c>
       <c r="E17">
-        <v>-24.21387939299322</v>
+        <v>-24.89993867668127</v>
       </c>
       <c r="F17">
-        <v>-2.455992696744247</v>
+        <v>-3.136325874459065</v>
       </c>
       <c r="G17">
-        <v>-7.271200609485088</v>
+        <v>-9.048903974254008</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.70367210055915</v>
       </c>
       <c r="E18">
-        <v>-27.8695398488992</v>
+        <v>-24.88683780137708</v>
       </c>
       <c r="F18">
-        <v>-2.627160738286917</v>
+        <v>-2.746523510825909</v>
       </c>
       <c r="G18">
-        <v>-8.824866115429369</v>
+        <v>-8.947770118574812</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.05155634582668</v>
       </c>
       <c r="E19">
-        <v>-27.26659617714793</v>
+        <v>-24.99686613434145</v>
       </c>
       <c r="F19">
-        <v>-2.501869340246089</v>
+        <v>-2.883933095602291</v>
       </c>
       <c r="G19">
-        <v>-7.904160363866042</v>
+        <v>-8.943886848657247</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.51880759150274</v>
       </c>
       <c r="E20">
-        <v>-24.27879959636718</v>
+        <v>-26.33395242679421</v>
       </c>
       <c r="F20">
-        <v>-2.785927291442276</v>
+        <v>-2.231456256908816</v>
       </c>
       <c r="G20">
-        <v>-8.159529225674342</v>
+        <v>-9.357572619244575</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.13678880883779</v>
       </c>
       <c r="E21">
-        <v>-27.77463209064644</v>
+        <v>-27.47163189479322</v>
       </c>
       <c r="F21">
-        <v>-2.387912493377767</v>
+        <v>-2.000835458499822</v>
       </c>
       <c r="G21">
-        <v>-7.841051434250915</v>
+        <v>-9.043924913762945</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.90782017066082</v>
       </c>
       <c r="E22">
-        <v>-27.48774873378652</v>
+        <v>-27.76288975754455</v>
       </c>
       <c r="F22">
-        <v>-2.559520398011324</v>
+        <v>-1.887813838429261</v>
       </c>
       <c r="G22">
-        <v>-7.626839274586834</v>
+        <v>-8.495956795011699</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.80877905069003</v>
       </c>
       <c r="E23">
-        <v>-28.62747507203699</v>
+        <v>-27.69905185945843</v>
       </c>
       <c r="F23">
-        <v>-2.172177457197081</v>
+        <v>-1.602926691462871</v>
       </c>
       <c r="G23">
-        <v>-7.107795392212201</v>
+        <v>-9.483628261743403</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.8354626512205</v>
       </c>
       <c r="E24">
-        <v>-29.57567186637005</v>
+        <v>-28.8143968936516</v>
       </c>
       <c r="F24">
-        <v>-1.407653158498736</v>
+        <v>-1.49922006283679</v>
       </c>
       <c r="G24">
-        <v>-7.899754027753272</v>
+        <v>-8.672293003160979</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.96600803872812</v>
       </c>
       <c r="E25">
-        <v>-29.40266378114401</v>
+        <v>-28.12608242990773</v>
       </c>
       <c r="F25">
-        <v>-1.577407176884827</v>
+        <v>-1.359890322420719</v>
       </c>
       <c r="G25">
-        <v>-7.153941086484102</v>
+        <v>-9.846434257937673</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.162736552383</v>
       </c>
       <c r="E26">
-        <v>-28.09681490239616</v>
+        <v>-28.76795286422893</v>
       </c>
       <c r="F26">
-        <v>-1.105559163841395</v>
+        <v>-1.41769711325768</v>
       </c>
       <c r="G26">
-        <v>-7.884234190265169</v>
+        <v>-8.631199201382005</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.39474848700804</v>
       </c>
       <c r="E27">
-        <v>-28.82724870288537</v>
+        <v>-30.10669431393151</v>
       </c>
       <c r="F27">
-        <v>-0.9846547995657933</v>
+        <v>-1.570793491540876</v>
       </c>
       <c r="G27">
-        <v>-8.425382585205515</v>
+        <v>-8.607167951312436</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.64480337150515</v>
       </c>
       <c r="E28">
-        <v>-28.71428139029003</v>
+        <v>-29.567964403609</v>
       </c>
       <c r="F28">
-        <v>-1.11149027444544</v>
+        <v>-1.816978485081069</v>
       </c>
       <c r="G28">
-        <v>-7.92878751213268</v>
+        <v>-9.553874727541199</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.88853886318647</v>
       </c>
       <c r="E29">
-        <v>-30.06752074952815</v>
+        <v>-28.83211681244362</v>
       </c>
       <c r="F29">
-        <v>-1.70710880297816</v>
+        <v>-1.363128410598262</v>
       </c>
       <c r="G29">
-        <v>-8.384801917985129</v>
+        <v>-9.140036671859065</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.09619892125401</v>
       </c>
       <c r="E30">
-        <v>-29.20663066982597</v>
+        <v>-29.5468866213403</v>
       </c>
       <c r="F30">
-        <v>-1.31618648661642</v>
+        <v>-1.475911460856818</v>
       </c>
       <c r="G30">
-        <v>-7.426703554555734</v>
+        <v>-9.121358573926496</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.27359190878282</v>
       </c>
       <c r="E31">
-        <v>-28.91237948575557</v>
+        <v>-30.30949975812802</v>
       </c>
       <c r="F31">
-        <v>-1.610116092151768</v>
+        <v>-1.383518674218172</v>
       </c>
       <c r="G31">
-        <v>-8.345260762064074</v>
+        <v>-9.32684082500352</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.42060766875604</v>
       </c>
       <c r="E32">
-        <v>-28.30744781391493</v>
+        <v>-29.41831418731452</v>
       </c>
       <c r="F32">
-        <v>-1.223451584240418</v>
+        <v>-1.47144987402534</v>
       </c>
       <c r="G32">
-        <v>-8.077808409037434</v>
+        <v>-9.087653909791177</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.53198838785889</v>
       </c>
       <c r="E33">
-        <v>-30.18052655415256</v>
+        <v>-29.50507522082748</v>
       </c>
       <c r="F33">
-        <v>-1.595180627879293</v>
+        <v>-1.374652657906009</v>
       </c>
       <c r="G33">
-        <v>-7.889895223137322</v>
+        <v>-8.429865063865689</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.62314761311943</v>
       </c>
       <c r="E34">
-        <v>-27.74754275913256</v>
+        <v>-28.57330999443125</v>
       </c>
       <c r="F34">
-        <v>-1.844969019621665</v>
+        <v>-1.550584640382179</v>
       </c>
       <c r="G34">
-        <v>-7.999414690667492</v>
+        <v>-8.69872770929206</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.71175280273743</v>
       </c>
       <c r="E35">
-        <v>-28.86890160680792</v>
+        <v>-28.56354660447071</v>
       </c>
       <c r="F35">
-        <v>-1.402218239968968</v>
+        <v>-1.618972168055098</v>
       </c>
       <c r="G35">
-        <v>-8.615937586445964</v>
+        <v>-9.293291756508546</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.80406564473281</v>
       </c>
       <c r="E36">
-        <v>-26.40395357800478</v>
+        <v>-28.802822114088</v>
       </c>
       <c r="F36">
-        <v>-1.480797171798529</v>
+        <v>-1.67810186163433</v>
       </c>
       <c r="G36">
-        <v>-7.973764583829219</v>
+        <v>-8.913903237708068</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.90224861850381</v>
       </c>
       <c r="E37">
-        <v>-28.03290907719991</v>
+        <v>-28.3094946841664</v>
       </c>
       <c r="F37">
-        <v>-2.010035306875314</v>
+        <v>-1.882369807858062</v>
       </c>
       <c r="G37">
-        <v>-8.661199365058881</v>
+        <v>-9.050317577199277</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.02287400986336</v>
       </c>
       <c r="E38">
-        <v>-25.47998185537575</v>
+        <v>-27.45537014463168</v>
       </c>
       <c r="F38">
-        <v>-1.378030740174625</v>
+        <v>-1.686738420175917</v>
       </c>
       <c r="G38">
-        <v>-7.970344790287151</v>
+        <v>-8.995465148159093</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.16637996902051</v>
       </c>
       <c r="E39">
-        <v>-26.56350530271703</v>
+        <v>-27.18867472489794</v>
       </c>
       <c r="F39">
-        <v>-1.245666741248695</v>
+        <v>-1.579830151538016</v>
       </c>
       <c r="G39">
-        <v>-8.189049360248024</v>
+        <v>-8.028530938685382</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.31441458260767</v>
       </c>
       <c r="E40">
-        <v>-26.28457394621458</v>
+        <v>-27.1816782325561</v>
       </c>
       <c r="F40">
-        <v>-1.663462952892057</v>
+        <v>-1.764799622378729</v>
       </c>
       <c r="G40">
-        <v>-7.695854217444021</v>
+        <v>-8.647728755259585</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.47309915838559</v>
       </c>
       <c r="E41">
-        <v>-25.04616310238895</v>
+        <v>-27.21581839809992</v>
       </c>
       <c r="F41">
-        <v>-2.033671942346795</v>
+        <v>-1.635606613870715</v>
       </c>
       <c r="G41">
-        <v>-7.101561634961754</v>
+        <v>-8.479612631684317</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.63468001490736</v>
       </c>
       <c r="E42">
-        <v>-26.52512648550202</v>
+        <v>-26.46073158511295</v>
       </c>
       <c r="F42">
-        <v>-1.590308170816027</v>
+        <v>-1.92888429426006</v>
       </c>
       <c r="G42">
-        <v>-7.324311691571615</v>
+        <v>-8.443597206762586</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.77874577512155</v>
       </c>
       <c r="E43">
-        <v>-24.90722951983362</v>
+        <v>-27.8101443838146</v>
       </c>
       <c r="F43">
-        <v>-1.501727530965064</v>
+        <v>-1.553540255275368</v>
       </c>
       <c r="G43">
-        <v>-7.125920629039711</v>
+        <v>-8.004128907515414</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.89886506550526</v>
       </c>
       <c r="E44">
-        <v>-24.54606560382588</v>
+        <v>-24.62455311532682</v>
       </c>
       <c r="F44">
-        <v>-1.843635348103158</v>
+        <v>-1.839314583730155</v>
       </c>
       <c r="G44">
-        <v>-8.336653343661968</v>
+        <v>-8.506874974200215</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.99430112845916</v>
       </c>
       <c r="E45">
-        <v>-24.31144989396248</v>
+        <v>-24.99118289946182</v>
       </c>
       <c r="F45">
-        <v>-1.482630348860924</v>
+        <v>-1.935207222645629</v>
       </c>
       <c r="G45">
-        <v>-7.591429679498789</v>
+        <v>-8.080062890549677</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.05456079923111</v>
       </c>
       <c r="E46">
-        <v>-24.35808411929347</v>
+        <v>-25.28572390586871</v>
       </c>
       <c r="F46">
-        <v>-1.386420445230179</v>
+        <v>-1.58224898435419</v>
       </c>
       <c r="G46">
-        <v>-8.087256706006514</v>
+        <v>-7.480672067936933</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.06712257038615</v>
       </c>
       <c r="E47">
-        <v>-24.14967921698647</v>
+        <v>-24.00736739282143</v>
       </c>
       <c r="F47">
-        <v>-1.379481211496927</v>
+        <v>-1.36852191075789</v>
       </c>
       <c r="G47">
-        <v>-7.418999915085849</v>
+        <v>-7.965968249084235</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.04322441597918</v>
       </c>
       <c r="E48">
-        <v>-22.93672292555796</v>
+        <v>-23.92047503356225</v>
       </c>
       <c r="F48">
-        <v>-1.340223223543453</v>
+        <v>-2.072569590480051</v>
       </c>
       <c r="G48">
-        <v>-6.979769975117505</v>
+        <v>-8.571225358392569</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.9831748608289</v>
       </c>
       <c r="E49">
-        <v>-21.845120680587</v>
+        <v>-23.7661808671729</v>
       </c>
       <c r="F49">
-        <v>-1.52330318833838</v>
+        <v>-1.734428359922487</v>
       </c>
       <c r="G49">
-        <v>-7.595534755967486</v>
+        <v>-7.835145421008855</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.87539030184649</v>
       </c>
       <c r="E50">
-        <v>-21.8369739558472</v>
+        <v>-23.3510194270977</v>
       </c>
       <c r="F50">
-        <v>-1.922692247924134</v>
+        <v>-1.597067648822871</v>
       </c>
       <c r="G50">
-        <v>-7.465883861013008</v>
+        <v>-8.358304311488803</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.7363289067096</v>
       </c>
       <c r="E51">
-        <v>-21.71534367247518</v>
+        <v>-22.21049154894787</v>
       </c>
       <c r="F51">
-        <v>-1.748440194540841</v>
+        <v>-1.902656525552622</v>
       </c>
       <c r="G51">
-        <v>-6.14217877986312</v>
+        <v>-7.347803322718283</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.57297299633867</v>
       </c>
       <c r="E52">
-        <v>-20.98803904752527</v>
+        <v>-22.52468613254805</v>
       </c>
       <c r="F52">
-        <v>-1.756080227096861</v>
+        <v>-2.019019779726077</v>
       </c>
       <c r="G52">
-        <v>-8.541086151803043</v>
+        <v>-8.026733312457557</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.38139186563709</v>
       </c>
       <c r="E53">
-        <v>-21.78179902853774</v>
+        <v>-21.53319939093867</v>
       </c>
       <c r="F53">
-        <v>-1.783692197734377</v>
+        <v>-1.629191736703435</v>
       </c>
       <c r="G53">
-        <v>-7.652942926163988</v>
+        <v>-8.378300006546</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.16740328495859</v>
       </c>
       <c r="E54">
-        <v>-21.40248498870726</v>
+        <v>-21.23595035707518</v>
       </c>
       <c r="F54">
-        <v>-1.819184427474724</v>
+        <v>-1.618537275168628</v>
       </c>
       <c r="G54">
-        <v>-7.991005904997743</v>
+        <v>-8.965438500117903</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.94373155560872</v>
       </c>
       <c r="E55">
-        <v>-20.65288215774358</v>
+        <v>-21.68192353429858</v>
       </c>
       <c r="F55">
-        <v>-1.26432157515974</v>
+        <v>-1.893233017978375</v>
       </c>
       <c r="G55">
-        <v>-8.515412871145996</v>
+        <v>-8.229093719091049</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.71119077237009</v>
       </c>
       <c r="E56">
-        <v>-19.1924583472179</v>
+        <v>-20.90236031930015</v>
       </c>
       <c r="F56">
-        <v>-2.475469271118869</v>
+        <v>-1.703634630090819</v>
       </c>
       <c r="G56">
-        <v>-6.208197679007267</v>
+        <v>-8.242282932519505</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.46281235642074</v>
       </c>
       <c r="E57">
-        <v>-19.36752915235444</v>
+        <v>-20.62823367371983</v>
       </c>
       <c r="F57">
-        <v>-1.831748275872985</v>
+        <v>-1.816792930782842</v>
       </c>
       <c r="G57">
-        <v>-8.067942983330406</v>
+        <v>-8.702965207582325</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.21510285874957</v>
       </c>
       <c r="E58">
-        <v>-20.09656818284929</v>
+        <v>-20.14420772940998</v>
       </c>
       <c r="F58">
-        <v>-0.8653268184577189</v>
+        <v>-1.739329809844852</v>
       </c>
       <c r="G58">
-        <v>-7.64829492022685</v>
+        <v>-8.621247701490956</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.96977335302831</v>
       </c>
       <c r="E59">
-        <v>-19.27851746725967</v>
+        <v>-20.65149191622323</v>
       </c>
       <c r="F59">
-        <v>-1.948135552701121</v>
+        <v>-1.648516719843345</v>
       </c>
       <c r="G59">
-        <v>-7.973996322016967</v>
+        <v>-8.57907466186618</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.71698320582336</v>
       </c>
       <c r="E60">
-        <v>-17.5208355659225</v>
+        <v>-19.3097684663866</v>
       </c>
       <c r="F60">
-        <v>-1.873995841783162</v>
+        <v>-1.853106900986767</v>
       </c>
       <c r="G60">
-        <v>-8.168514046267925</v>
+        <v>-8.349392322897085</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.46806281857058</v>
       </c>
       <c r="E61">
-        <v>-18.08268333605416</v>
+        <v>-18.83922378919759</v>
       </c>
       <c r="F61">
-        <v>-1.037309145157341</v>
+        <v>-1.879912870141359</v>
       </c>
       <c r="G61">
-        <v>-8.326354236489296</v>
+        <v>-8.29235824434652</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.22707484989616</v>
       </c>
       <c r="E62">
-        <v>-17.95256216391776</v>
+        <v>-18.9408925591438</v>
       </c>
       <c r="F62">
-        <v>-1.382325825158141</v>
+        <v>-2.255713339564994</v>
       </c>
       <c r="G62">
-        <v>-9.125089558749256</v>
+        <v>-8.320219795605027</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.98763206307061</v>
       </c>
       <c r="E63">
-        <v>-18.60128870788658</v>
+        <v>-19.63037084070764</v>
       </c>
       <c r="F63">
-        <v>-2.101669308972995</v>
+        <v>-1.908904072504536</v>
       </c>
       <c r="G63">
-        <v>-8.697506117988068</v>
+        <v>-9.120679912090946</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.74918658985832</v>
       </c>
       <c r="E64">
-        <v>-17.6269875251363</v>
+        <v>-18.1725644881584</v>
       </c>
       <c r="F64">
-        <v>-2.155849507320499</v>
+        <v>-1.753116328529644</v>
       </c>
       <c r="G64">
-        <v>-8.852969336512242</v>
+        <v>-8.716703971570301</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.52071994729324</v>
       </c>
       <c r="E65">
-        <v>-17.9675785837272</v>
+        <v>-18.71094117750831</v>
       </c>
       <c r="F65">
-        <v>-1.515615938840401</v>
+        <v>-2.618853041604241</v>
       </c>
       <c r="G65">
-        <v>-7.617192344885398</v>
+        <v>-9.009276744148933</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.30077356853989</v>
       </c>
       <c r="E66">
-        <v>-17.42494060033607</v>
+        <v>-18.16558158123857</v>
       </c>
       <c r="F66">
-        <v>-1.572474249001156</v>
+        <v>-1.874936867152742</v>
       </c>
       <c r="G66">
-        <v>-8.683092002710081</v>
+        <v>-8.976379853125193</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.07974390368663</v>
       </c>
       <c r="E67">
-        <v>-17.13041770782521</v>
+        <v>-17.97076210095459</v>
       </c>
       <c r="F67">
-        <v>-1.809662344179544</v>
+        <v>-2.278844670920767</v>
       </c>
       <c r="G67">
-        <v>-8.641058005997955</v>
+        <v>-9.667237738442463</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.87178526376886</v>
       </c>
       <c r="E68">
-        <v>-17.98917034779577</v>
+        <v>-17.91585435361159</v>
       </c>
       <c r="F68">
-        <v>-2.588739401410271</v>
+        <v>-1.975645634148092</v>
       </c>
       <c r="G68">
-        <v>-8.679639103712621</v>
+        <v>-9.305431527001053</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.679013938626642</v>
       </c>
       <c r="E69">
-        <v>-18.39262568256114</v>
+        <v>-17.24105738478061</v>
       </c>
       <c r="F69">
-        <v>-1.979660730949461</v>
+        <v>-2.27931021340114</v>
       </c>
       <c r="G69">
-        <v>-7.61668252087235</v>
+        <v>-8.847493694190288</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.494554920581153</v>
       </c>
       <c r="E70">
-        <v>-16.67899677637059</v>
+        <v>-17.294420922487</v>
       </c>
       <c r="F70">
-        <v>-2.009990575035562</v>
+        <v>-1.656014273206083</v>
       </c>
       <c r="G70">
-        <v>-8.766408502296919</v>
+        <v>-9.886634212421043</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.327329009678675</v>
       </c>
       <c r="E71">
-        <v>-17.58321076690415</v>
+        <v>-18.09031834323109</v>
       </c>
       <c r="F71">
-        <v>-1.640349845619145</v>
+        <v>-2.590138513953599</v>
       </c>
       <c r="G71">
-        <v>-8.653098460124284</v>
+        <v>-9.630397987681453</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.185062617169136</v>
       </c>
       <c r="E72">
-        <v>-16.19562293231785</v>
+        <v>-17.68216698091976</v>
       </c>
       <c r="F72">
-        <v>-1.987565012706974</v>
+        <v>-1.866242322892959</v>
       </c>
       <c r="G72">
-        <v>-8.89968113407136</v>
+        <v>-10.10017433134065</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.066634959998375</v>
       </c>
       <c r="E73">
-        <v>-18.09524532295144</v>
+        <v>-18.65194421813638</v>
       </c>
       <c r="F73">
-        <v>-1.82045845654023</v>
+        <v>-2.124773304204476</v>
       </c>
       <c r="G73">
-        <v>-8.28795521877929</v>
+        <v>-9.325834419159582</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.970548402180386</v>
       </c>
       <c r="E74">
-        <v>-18.26693788647825</v>
+        <v>-17.68049597401093</v>
       </c>
       <c r="F74">
-        <v>-2.218098004171271</v>
+        <v>-2.493593949892122</v>
       </c>
       <c r="G74">
-        <v>-8.967822092906179</v>
+        <v>-9.193733720506044</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.908241626808666</v>
       </c>
       <c r="E75">
-        <v>-19.59340490738303</v>
+        <v>-18.07954963204085</v>
       </c>
       <c r="F75">
-        <v>-1.794247255180848</v>
+        <v>-2.430445017674508</v>
       </c>
       <c r="G75">
-        <v>-7.958976376905294</v>
+        <v>-9.346045299676833</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.880186429764894</v>
       </c>
       <c r="E76">
-        <v>-18.1294670010274</v>
+        <v>-18.60722553731063</v>
       </c>
       <c r="F76">
-        <v>-2.077829723487828</v>
+        <v>-2.609938979982716</v>
       </c>
       <c r="G76">
-        <v>-8.394422363322251</v>
+        <v>-9.896224862848312</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.874347789073779</v>
       </c>
       <c r="E77">
-        <v>-17.79311912258169</v>
+        <v>-19.05999142554553</v>
       </c>
       <c r="F77">
-        <v>-2.692118824912246</v>
+        <v>-2.745885667925754</v>
       </c>
       <c r="G77">
-        <v>-7.505239626383864</v>
+        <v>-8.932485329819997</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.898733806781191</v>
       </c>
       <c r="E78">
-        <v>-18.40855685412013</v>
+        <v>-19.19744872557436</v>
       </c>
       <c r="F78">
-        <v>-2.979597933481995</v>
+        <v>-2.667873339399708</v>
       </c>
       <c r="G78">
-        <v>-8.248453789404707</v>
+        <v>-9.465983054019089</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.95048555501571</v>
       </c>
       <c r="E79">
-        <v>-19.40254784185575</v>
+        <v>-18.86948758099085</v>
       </c>
       <c r="F79">
-        <v>-2.067468504013612</v>
+        <v>-2.594693706301594</v>
       </c>
       <c r="G79">
-        <v>-8.342688468180061</v>
+        <v>-9.500992073096882</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.017796880923967</v>
       </c>
       <c r="E80">
-        <v>-18.81875961515693</v>
+        <v>-19.77881421867908</v>
       </c>
       <c r="F80">
-        <v>-2.886968233766149</v>
+        <v>-2.824765297122531</v>
       </c>
       <c r="G80">
-        <v>-8.178362919247256</v>
+        <v>-8.96368060043655</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.09798381737666</v>
       </c>
       <c r="E81">
-        <v>-18.8500332566539</v>
+        <v>-20.15350015807372</v>
       </c>
       <c r="F81">
-        <v>-3.03108262430079</v>
+        <v>-2.612904535284738</v>
       </c>
       <c r="G81">
-        <v>-8.358651918770427</v>
+        <v>-8.669621392910786</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.193217401599444</v>
       </c>
       <c r="E82">
-        <v>-19.60924550946186</v>
+        <v>-21.02412645689239</v>
       </c>
       <c r="F82">
-        <v>-2.900478906105809</v>
+        <v>-2.74731377332818</v>
       </c>
       <c r="G82">
-        <v>-8.270945635798515</v>
+        <v>-9.958002953156651</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.297910136704141</v>
       </c>
       <c r="E83">
-        <v>-21.07644391710301</v>
+        <v>-22.12477659293068</v>
       </c>
       <c r="F83">
-        <v>-3.2986660045901</v>
+        <v>-2.883053369420518</v>
       </c>
       <c r="G83">
-        <v>-7.812882002257257</v>
+        <v>-8.906610105885054</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.401508386609514</v>
       </c>
       <c r="E84">
-        <v>-21.6449213731819</v>
+        <v>-23.02003326187707</v>
       </c>
       <c r="F84">
-        <v>-2.592741244333195</v>
+        <v>-2.924238139952904</v>
       </c>
       <c r="G84">
-        <v>-8.090656636275344</v>
+        <v>-8.645017418462922</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.512356947294167</v>
       </c>
       <c r="E85">
-        <v>-23.00309676908839</v>
+        <v>-23.33992466577891</v>
       </c>
       <c r="F85">
-        <v>-2.520387493535672</v>
+        <v>-2.653122601058057</v>
       </c>
       <c r="G85">
-        <v>-7.019165467034832</v>
+        <v>-9.368606667526965</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.629365674476899</v>
       </c>
       <c r="E86">
-        <v>-24.19047623932158</v>
+        <v>-24.40658860438963</v>
       </c>
       <c r="F86">
-        <v>-2.886315480252743</v>
+        <v>-3.251720767138647</v>
       </c>
       <c r="G86">
-        <v>-9.141864092996743</v>
+        <v>-9.121924677213713</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.741207798452015</v>
       </c>
       <c r="E87">
-        <v>-24.56960914019175</v>
+        <v>-25.23936591745219</v>
       </c>
       <c r="F87">
-        <v>-2.983804383153411</v>
+        <v>-3.091071334876724</v>
       </c>
       <c r="G87">
-        <v>-8.650479818602721</v>
+        <v>-9.141417169348941</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.855904980389532</v>
       </c>
       <c r="E88">
-        <v>-24.59159035302499</v>
+        <v>-25.0257668554584</v>
       </c>
       <c r="F88">
-        <v>-3.232905229951459</v>
+        <v>-3.564558687010297</v>
       </c>
       <c r="G88">
-        <v>-7.142784548016758</v>
+        <v>-9.445527193131932</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.977832366785311</v>
       </c>
       <c r="E89">
-        <v>-26.046308286301</v>
+        <v>-27.40901668468916</v>
       </c>
       <c r="F89">
-        <v>-2.980304530876583</v>
+        <v>-3.422854845617802</v>
       </c>
       <c r="G89">
-        <v>-7.435946597701379</v>
+        <v>-9.510493338794589</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.10330805023034</v>
       </c>
       <c r="E90">
-        <v>-28.65142164258955</v>
+        <v>-28.56921625392831</v>
       </c>
       <c r="F90">
-        <v>-3.511104138507644</v>
+        <v>-3.529801219156232</v>
       </c>
       <c r="G90">
-        <v>-9.456127559948678</v>
+        <v>-9.516425836400963</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.23317951522742</v>
       </c>
       <c r="E91">
-        <v>-31.28371489987215</v>
+        <v>-29.44987765114799</v>
       </c>
       <c r="F91">
-        <v>-4.192612769567035</v>
+        <v>-3.362571236246471</v>
       </c>
       <c r="G91">
-        <v>-9.544300629841628</v>
+        <v>-9.589221422263998</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.37843419055592</v>
       </c>
       <c r="E92">
-        <v>-30.03409834711454</v>
+        <v>-30.89547523777255</v>
       </c>
       <c r="F92">
-        <v>-3.813741542181222</v>
+        <v>-3.712882840685965</v>
       </c>
       <c r="G92">
-        <v>-10.5580260899674</v>
+        <v>-10.4675223960148</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.54067006123308</v>
       </c>
       <c r="E93">
-        <v>-32.31120753831652</v>
+        <v>-32.59389979248235</v>
       </c>
       <c r="F93">
-        <v>-3.63283521345124</v>
+        <v>-3.338894839139655</v>
       </c>
       <c r="G93">
-        <v>-9.41482850434627</v>
+        <v>-10.04247483313669</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.70947552972215</v>
       </c>
       <c r="E94">
-        <v>-35.08847536248068</v>
+        <v>-34.1826016862233</v>
       </c>
       <c r="F94">
-        <v>-3.366277352006596</v>
+        <v>-3.764824790311105</v>
       </c>
       <c r="G94">
-        <v>-9.762846293616615</v>
+        <v>-10.42215136939909</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.89678819561638</v>
       </c>
       <c r="E95">
-        <v>-36.47925577124239</v>
+        <v>-35.57216619971395</v>
       </c>
       <c r="F95">
-        <v>-3.342628291024073</v>
+        <v>-3.773436497830609</v>
       </c>
       <c r="G95">
-        <v>-9.985569865862162</v>
+        <v>-9.914499074225088</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.10067728796034</v>
       </c>
       <c r="E96">
-        <v>-37.07650488692902</v>
+        <v>-38.27917022117509</v>
       </c>
       <c r="F96">
-        <v>-3.853890853460108</v>
+        <v>-3.7750021122219</v>
       </c>
       <c r="G96">
-        <v>-9.137960959805943</v>
+        <v>-10.97882622291862</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.30453125783295</v>
       </c>
       <c r="E97">
-        <v>-38.04280199187073</v>
+        <v>-38.97969345084365</v>
       </c>
       <c r="F97">
-        <v>-3.672682998995508</v>
+        <v>-3.881638676351683</v>
       </c>
       <c r="G97">
-        <v>-10.08734265683044</v>
+        <v>-10.75473870591089</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.50708535446714</v>
       </c>
       <c r="E98">
-        <v>-41.29302816986998</v>
+        <v>-41.39443202408675</v>
       </c>
       <c r="F98">
-        <v>-3.967965328499628</v>
+        <v>-3.86608524999672</v>
       </c>
       <c r="G98">
-        <v>-9.229861703976111</v>
+        <v>-10.88358513829932</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.70017204797808</v>
       </c>
       <c r="E99">
-        <v>-44.41874395502834</v>
+        <v>-43.97372628582057</v>
       </c>
       <c r="F99">
-        <v>-4.342538157432314</v>
+        <v>-3.886575746072368</v>
       </c>
       <c r="G99">
-        <v>-10.61329564774553</v>
+        <v>-11.17422455228302</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.87004489612252</v>
       </c>
       <c r="E100">
-        <v>-45.36448178797524</v>
+        <v>-45.35357722256477</v>
       </c>
       <c r="F100">
-        <v>-4.065090578110468</v>
+        <v>-4.233388326602437</v>
       </c>
       <c r="G100">
-        <v>-10.2240483243291</v>
+        <v>-10.97490653700012</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.99439310485152</v>
       </c>
       <c r="E101">
-        <v>-47.8360481815406</v>
+        <v>-46.76110166396985</v>
       </c>
       <c r="F101">
-        <v>-3.843171779267883</v>
+        <v>-4.046924480967074</v>
       </c>
       <c r="G101">
-        <v>-9.306110188836604</v>
+        <v>-11.70058474029944</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.07977880252327</v>
       </c>
       <c r="E102">
-        <v>-50.11854965316721</v>
+        <v>-49.08435826954699</v>
       </c>
       <c r="F102">
-        <v>-4.127566047629606</v>
+        <v>-4.309869003800707</v>
       </c>
       <c r="G102">
-        <v>-9.500237268713928</v>
+        <v>-10.91415802635449</v>
       </c>
     </row>
   </sheetData>
